--- a/order_forms/011_team_apparel_order_form--order_forms.xlsx
+++ b/order_forms/011_team_apparel_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_2</t>
+          <t>select_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_3</t>
+          <t>select_size</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4</t>
+          <t>select_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_5</t>
+          <t>select_quantity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_6</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_7</t>
+          <t>team_size</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_8</t>
+          <t>team_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_9</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_10</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_11</t>
+          <t>size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method (2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>team_size_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Team Size (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>team_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>Team Name (2)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments (2)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Team (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>size_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Size (2)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,568 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Type (2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>quantity_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>payment_method_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>team_size_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>team_name_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Team Name</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>team_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>size_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>type_2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>quantity_3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>payment_method_3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>team_size_3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>team_name_3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Team Name</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>comments_3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>team_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>size_3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>type_3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>quantity_4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>payment_method_4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>team_size_4</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>team_name_4</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Team Name</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>comments_4</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>team_4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>size_4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>type_4</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1535,10 +983,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1563,7 +1011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_2_choices</t>
+          <t>select_team_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1580,7 +1028,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_2_choices</t>
+          <t>select_team_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1597,7 +1045,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_2_choices</t>
+          <t>select_team_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1614,7 +1062,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_3_choices</t>
+          <t>select_size_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1631,7 +1079,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_3_choices</t>
+          <t>select_size_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1648,7 +1096,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_3_choices</t>
+          <t>select_size_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1665,7 +1113,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_3_choices</t>
+          <t>select_size_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1682,7 +1130,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4_choices</t>
+          <t>select_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1699,7 +1147,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4_choices</t>
+          <t>select_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1716,7 +1164,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4_choices</t>
+          <t>select_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1733,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4_choices</t>
+          <t>select_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1750,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_4_choices</t>
+          <t>select_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1767,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_6_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1784,7 +1232,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_6_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1801,7 +1249,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_10_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1818,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_10_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1835,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_10_choices</t>
+          <t>team_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1852,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_11_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1869,7 +1317,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_11_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1886,7 +1334,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_11_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1903,7 +1351,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_11_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1920,7 +1368,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12_choices</t>
+          <t>type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1937,7 +1385,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12_choices</t>
+          <t>type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12_choices</t>
+          <t>type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1971,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12_choices</t>
+          <t>type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,7 +1436,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>team_apparel_order_form_12_choices</t>
+          <t>type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2005,7 +1453,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2022,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2039,7 +1487,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_choices</t>
+          <t>team_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2056,7 +1504,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_choices</t>
+          <t>team_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2073,7 +1521,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_choices</t>
+          <t>team_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2090,7 +1538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>size_choices</t>
+          <t>size_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2107,7 +1555,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>size_choices</t>
+          <t>size_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2124,7 +1572,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>size_choices</t>
+          <t>size_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2141,7 +1589,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>size_choices</t>
+          <t>size_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2158,7 +1606,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>type_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2175,7 +1623,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>type_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2192,7 +1640,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>type_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2209,7 +1657,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>type_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2226,7 +1674,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>type_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2235,720 +1683,6 @@
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>Sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>payment_method_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>payment_method_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>team_2_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>team_a</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Team A</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>team_2_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>team_b</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Team B</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>team_2_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>team_c</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Team C</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>size_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>size_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>size_2_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>size_2_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>extra_large</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Extra Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>type_2_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>short_sleeve</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Short Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>type_2_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>long_sleeve</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Long Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>type_2_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>hoodie</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Hoodie</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>type_2_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>jersey</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>type_2_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>sweatshirt</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>payment_method_3_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>payment_method_3_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>team_3_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>team_a</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Team A</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>team_3_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>team_b</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Team B</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>team_3_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>team_c</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Team C</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>size_3_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>size_3_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>size_3_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>size_3_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>extra_large</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Extra Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>type_3_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>short_sleeve</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Short Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>type_3_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>long_sleeve</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Long Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>type_3_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>hoodie</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Hoodie</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>type_3_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>jersey</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>type_3_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>sweatshirt</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>payment_method_4_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>payment_method_4_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>team_4_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>team_a</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Team A</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>team_4_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>team_b</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Team B</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>team_4_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>team_c</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Team C</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>size_4_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>size_4_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>size_4_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>size_4_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>extra_large</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Extra Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>type_4_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>short_sleeve</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Short Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>type_4_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>long_sleeve</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Long Sleeve</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>type_4_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>hoodie</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Hoodie</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>type_4_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>jersey</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>type_4_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>sweatshirt</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
         <is>
           <t>Sweatshirt</t>
         </is>
